--- a/#Uacf5#Uc9c0#Uc0ac#Ud56d.xlsx
+++ b/#Uacf5#Uc9c0#Uc0ac#Ud56d.xlsx
@@ -20,265 +20,160 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
+  <x:si>
+    <x:t>소그룹 모임 변경안내</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지사항 표준양식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>짧고 분명하게 작성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바자회 물품 후원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지/안내/행사/예배/교육/전도/봉사/회의/기타 중 선택</x:t>
+  </x:si>
+  <x:si>
+    <x:t>salvation land 어린이 캠프(7월25일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구세군사관대학원대학교에서 진행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>열 이름과 순서를 변경하지 마세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>남서울지방 여름성회(8/12~14)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수원역 생수나눔 봉사(8월1일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작성 방법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가정단에서 바자회 물품 후원을 받습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지 노출 종료일. 해당 날짜까지 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일정·장소·준비사항 등을 자세히 작성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Y</x:t>
+  </x:si>
+  <x:si>
+    <x:t>항목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시작일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주의</x:t>
+  </x:si>
+  <x:si>
+    <x:t>봉사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>행사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장소 : 과천영문 (세부일정 추후 공지예정)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소그룹 모임을 매월 첫째주와 셋째주로 변경 합니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지 노출 시작일. yyyy-mm-dd 형식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시작일·종료일 사이에만 앱에 표시됩니다. 중요=Y인 공지는 상단에 강조됩니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영문출발 오전10시30분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Y=중요공지, N=일반공지</x:t>
+  </x:si>
   <x:si>
     <x:t>영문출발은 오전10시 30분</x:t>
   </x:si>
   <x:si>
-    <x:t>시작일·종료일 사이에만 앱에 표시됩니다. 중요=Y인 공지는 상단에 강조됩니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시작일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중요</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>항목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주의</x:t>
-  </x:si>
-  <x:si>
-    <x:t>짧고 분명하게 작성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수원역 무료급식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소그룹 모임 변경안내</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소그룹 모임을 매월 첫째주와 셋째주로 변경 합니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Y=중요공지, N=일반공지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바자회 물품 후원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>열 이름과 순서를 변경하지 마세요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가정단에서 바자회 물품 후원을 받습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>N</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Y</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지 노출 시작일. yyyy-mm-dd 형식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일정·장소·준비사항 등을 자세히 작성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지 노출 종료일. 해당 날짜까지 표시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지사항 표준양식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작성 방법</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안내</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지/안내/행사/예배/교육/전도/봉사/회의/기타 중 선택</x:t>
-  </x:si>
-  <x:si>
-    <x:t>봉사</x:t>
+    <x:t>수원역 무료급식(7월14일)</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <x:numFmt numFmtId="165" formatCode="m&quot;월&quot;\ d&quot;일&quot;;@"/>
   </x:numFmts>
   <x:fonts count="9">
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ffffffff"/>
-          <x:b val="1"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Carlito"/>
-          <x:sz val="11"/>
-          <x:color rgb="ffffffff"/>
-          <x:b val="1"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Carlito"/>
-          <x:sz val="16"/>
-          <x:color rgb="ffffffff"/>
-          <x:b val="1"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Carlito"/>
-          <x:sz val="16"/>
-          <x:color rgb="ffffffff"/>
-          <x:b val="1"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="11"/>
+      <x:color rgb="ffffffff"/>
+      <x:b val="1"/>
+    </x:font>
+    <x:font>
+      <x:name val="Carlito"/>
+      <x:sz val="16"/>
+      <x:color rgb="ffffffff"/>
+      <x:b val="1"/>
+    </x:font>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:font hs:extension="1">
@@ -358,8 +253,8 @@
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+  <x:cellXfs count="32">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
@@ -496,6 +391,9 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
@@ -511,12 +409,6 @@
     </mc:AlternateContent>
     <x:xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -897,7 +789,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff8e1b33"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1103,7 +994,7 @@
   <x:sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="13.550000000000001"/>
   <x:cols>
     <x:col min="1" max="1" width="16.453125" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="13" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="17" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="12" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="41" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="52" style="1" customWidth="1"/>
@@ -1111,128 +1002,164 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:6" ht="32" customHeight="1">
-      <x:c r="A1" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
-      <x:c r="E1" s="29"/>
-      <x:c r="F1" s="29"/>
+      <x:c r="A1" s="30" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B1" s="30"/>
+      <x:c r="C1" s="30"/>
+      <x:c r="D1" s="30"/>
+      <x:c r="E1" s="30"/>
+      <x:c r="F1" s="30"/>
     </x:row>
     <x:row r="2" spans="1:6" ht="28" customHeight="1">
-      <x:c r="A2" s="30" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="30"/>
-      <x:c r="C2" s="30"/>
-      <x:c r="D2" s="30"/>
-      <x:c r="E2" s="30"/>
-      <x:c r="F2" s="30"/>
+      <x:c r="A2" s="31" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B2" s="31"/>
+      <x:c r="C2" s="31"/>
+      <x:c r="D2" s="31"/>
+      <x:c r="E2" s="31"/>
+      <x:c r="F2" s="31"/>
     </x:row>
     <x:row r="4" spans="1:6" ht="24" customHeight="1">
       <x:c r="A4" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D4" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E4" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F4" s="4" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:6">
+      <x:c r="A5" s="29">
+        <x:v>46217</x:v>
+      </x:c>
+      <x:c r="B5" s="29">
+        <x:v>46217</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D5" s="5" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E5" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:6">
+      <x:c r="A6" s="29">
+        <x:v>46217</x:v>
+      </x:c>
+      <x:c r="B6" s="18">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="16" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F6" s="5" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:6">
+      <x:c r="A7" s="29">
+        <x:v>46217</x:v>
+      </x:c>
+      <x:c r="B7" s="18">
+        <x:v>46222</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D7" s="5" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E7" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F7" s="5" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:6">
+      <x:c r="A8" s="29">
+        <x:v>46221</x:v>
+      </x:c>
+      <x:c r="B8" s="19">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C8" s="20" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D8" s="20" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E8" s="21" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F8" s="5" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:6">
+      <x:c r="A9" s="29">
+        <x:v>46221</x:v>
+      </x:c>
+      <x:c r="B9" s="18">
+        <x:v>46228</x:v>
+      </x:c>
+      <x:c r="C9" s="20" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D9" s="20" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E9" s="21" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="s">
+      <x:c r="F9" s="5" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:6">
+      <x:c r="A10" s="29">
+        <x:v>46221</x:v>
+      </x:c>
+      <x:c r="B10" s="18">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C10" s="20" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F4" s="4" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:6">
-      <x:c r="A5" s="32">
-        <x:v>46217</x:v>
-      </x:c>
-      <x:c r="B5" s="31">
-        <x:v>46217</x:v>
-      </x:c>
-      <x:c r="C5" s="5" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E5" s="15" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F5" s="6" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:6">
-      <x:c r="A6" s="32">
-        <x:v>46217</x:v>
-      </x:c>
-      <x:c r="B6" s="31">
-        <x:v>46234</x:v>
-      </x:c>
-      <x:c r="C6" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D6" s="9" t="s">
+      <x:c r="D10" s="20" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E10" s="21" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F10" s="5" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="E6" s="16" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F6" s="10" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:6">
-      <x:c r="A7" s="32">
-        <x:v>46217</x:v>
-      </x:c>
-      <x:c r="B7" s="31">
-        <x:v>46234</x:v>
-      </x:c>
-      <x:c r="C7" s="5" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D7" s="5" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E7" s="15" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F7" s="5" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:6">
-      <x:c r="A8" s="18"/>
-      <x:c r="B8" s="19"/>
-      <x:c r="C8" s="20"/>
-      <x:c r="D8" s="20"/>
-      <x:c r="E8" s="21"/>
-      <x:c r="F8" s="22"/>
-    </x:row>
-    <x:row r="9" spans="1:6">
-      <x:c r="A9" s="18"/>
-      <x:c r="B9" s="19"/>
-      <x:c r="C9" s="20"/>
-      <x:c r="D9" s="20"/>
-      <x:c r="E9" s="21"/>
-      <x:c r="F9" s="22"/>
-    </x:row>
-    <x:row r="10" spans="1:6">
-      <x:c r="A10" s="18"/>
-      <x:c r="B10" s="19"/>
-      <x:c r="C10" s="20"/>
-      <x:c r="D10" s="20"/>
-      <x:c r="E10" s="21"/>
-      <x:c r="F10" s="22"/>
     </x:row>
     <x:row r="11" spans="1:6">
       <x:c r="A11" s="18"/>
@@ -2751,17 +2678,32 @@
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="A5:A6 C5:F6 A8:F199">
-    <x:cfRule type="expression" dxfId="12" priority="3">
+  <x:conditionalFormatting sqref="A5:F5 A6:E10 A11:F199">
+    <x:cfRule type="expression" dxfId="12" priority="6">
       <x:formula>$F5="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="B5:B6">
-    <x:cfRule type="expression" dxfId="12" priority="2">
-      <x:formula>$F5="Y"</x:formula>
+  <x:conditionalFormatting sqref="F8:F8">
+    <x:cfRule type="expression" dxfId="12" priority="5">
+      <x:formula>$F8="Y"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="A7:F7">
+  <x:conditionalFormatting sqref="F9:F9">
+    <x:cfRule type="expression" dxfId="12" priority="4">
+      <x:formula>$F9="Y"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F10:F10">
+    <x:cfRule type="expression" dxfId="12" priority="3">
+      <x:formula>$F10="Y"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F6:F6">
+    <x:cfRule type="expression" dxfId="12" priority="2">
+      <x:formula>$F6="Y"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F7:F7">
     <x:cfRule type="expression" dxfId="12" priority="1">
       <x:formula>$F7="Y"</x:formula>
     </x:cfRule>
@@ -2774,7 +2716,7 @@
       <x:formula1>"Y,N"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
-  <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
@@ -2791,70 +2733,70 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="23" t="s">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B1" s="24" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="25" t="s">
-        <x:v>2</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B2" s="27" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="25" t="s">
-        <x:v>6</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B3" s="27" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="25" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B4" s="27" t="s">
-        <x:v>26</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="25" t="s">
-        <x:v>4</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B5" s="27" t="s">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="25" t="s">
-        <x:v>5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="27" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="25" t="s">
-        <x:v>3</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B7" s="27" t="s">
-        <x:v>13</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="26" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B8" s="28" t="s">
-        <x:v>15</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>